--- a/data/trans_dic/P5_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con algún problema medioambiental importante en la zona de residencia</t>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,37; 52,05</t>
+          <t>30,72; 51,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,36; 45,51</t>
+          <t>24,02; 44,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,37; 43,56</t>
+          <t>20,08; 42,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 23,91</t>
+          <t>7,08; 23,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,93; 53,44</t>
+          <t>32,0; 53,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,89; 46,1</t>
+          <t>26,44; 46,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,17; 51,72</t>
+          <t>30,3; 52,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,97; 34,96</t>
+          <t>14,86; 35,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,75; 49,86</t>
+          <t>33,78; 48,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,27; 42,67</t>
+          <t>28,56; 42,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,21; 44,02</t>
+          <t>27,87; 44,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 27,13</t>
+          <t>13,56; 28,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,7; 30,57</t>
+          <t>22,33; 30,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 42,81</t>
+          <t>33,25; 42,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,32; 38,75</t>
+          <t>30,03; 38,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,49; 37,04</t>
+          <t>16,73; 39,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 30,84</t>
+          <t>23,23; 30,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,9; 42,07</t>
+          <t>32,86; 41,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,28; 38,93</t>
+          <t>31,03; 38,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 18,93</t>
+          <t>12,69; 18,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,0; 29,4</t>
+          <t>23,93; 29,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,51; 40,68</t>
+          <t>34,48; 40,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,72; 37,52</t>
+          <t>32,02; 37,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,76; 27,27</t>
+          <t>15,82; 27,28</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,73; 33,6</t>
+          <t>21,57; 33,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,06; 48,09</t>
+          <t>32,91; 47,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,65; 45,18</t>
+          <t>32,02; 45,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,6; 25,64</t>
+          <t>15,36; 25,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,88; 31,84</t>
+          <t>19,31; 32,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,6; 49,01</t>
+          <t>35,26; 49,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,42; 49,69</t>
+          <t>36,44; 49,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,69; 24,44</t>
+          <t>14,05; 24,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,26; 30,55</t>
+          <t>21,81; 30,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,2; 46,47</t>
+          <t>35,81; 46,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,91; 45,57</t>
+          <t>35,23; 44,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,08; 23,51</t>
+          <t>15,78; 23,43</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,11; 31,24</t>
+          <t>25,01; 31,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,46; 41,73</t>
+          <t>34,63; 41,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,61; 38,46</t>
+          <t>31,7; 38,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,9; 31,97</t>
+          <t>17,06; 30,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,8; 31,05</t>
+          <t>24,75; 30,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,92; 41,77</t>
+          <t>34,62; 41,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,31; 40,94</t>
+          <t>33,9; 40,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,85</t>
+          <t>14,7; 19,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,76; 30,3</t>
+          <t>25,67; 30,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 40,49</t>
+          <t>35,66; 40,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,97; 38,42</t>
+          <t>33,78; 38,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,67; 25,18</t>
+          <t>16,79; 24,46</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>23180</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19122</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12298</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7546</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21644</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22342</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20814</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>14842</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>44825</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41465</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33112</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>22388</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>17345; 29090</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13327; 24918</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8159; 17247</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3874; 12969</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>16437; 27483</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>16416; 29153</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15524; 26806</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9212; 22153</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>36431; 52702</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>33574; 49471</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>25608; 40701</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>15823; 32711</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>81521</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>115363</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>118753</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>103515</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94974</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>126269</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>132938</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>81271</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>176495</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>241632</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>251691</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>184786</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>69307; 93989</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101303; 129861</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>104361; 133374</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>77054; 180260</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>82141; 107890</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>111657; 140235</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>117858; 148081</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>65541; 97172</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>158862; 196106</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>222206; 263659</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>232919; 273263</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>154557; 266577</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>36754</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>46922</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52411</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30009</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31029</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57530</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59642</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>34104</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>67783</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>104452</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>112053</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>64114</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>29457; 45857</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>38442; 55868</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43553; 62253</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22972; 38605</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23859; 39851</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>48277; 67388</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>50996; 69945</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>25629; 44246</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>56735; 78934</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>90870; 117310</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>97211; 124066</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>52369; 77764</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>141455</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>181408</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>183462</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>141069</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>130218</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>289103</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>387550</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>396856</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>271288</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>125887; 158034</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>165150; 199619</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166203; 201377</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>113404; 205224</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>130804; 162956</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>186550; 224109</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>193596; 231374</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>111905; 149274</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>264926; 311705</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>362249; 412672</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>369934; 423452</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>239320; 348796</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,72; 51,52</t>
+          <t>30,89; 52,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,02; 44,91</t>
+          <t>24,42; 46,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,08; 42,44</t>
+          <t>20,53; 42,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 23,72</t>
+          <t>6,95; 24,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,0; 53,5</t>
+          <t>30,44; 52,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,44; 46,95</t>
+          <t>26,77; 46,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,3; 52,32</t>
+          <t>30,28; 53,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,86; 35,73</t>
+          <t>15,13; 34,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,78; 48,87</t>
+          <t>34,01; 48,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,56; 42,08</t>
+          <t>29,14; 42,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,87; 44,3</t>
+          <t>29,13; 44,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 28,03</t>
+          <t>13,32; 26,57</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,33; 30,29</t>
+          <t>22,49; 30,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,25; 42,63</t>
+          <t>33,44; 42,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,03; 38,37</t>
+          <t>30,16; 38,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 39,14</t>
+          <t>16,69; 38,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 30,51</t>
+          <t>23,32; 30,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,86; 41,27</t>
+          <t>32,92; 41,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,03; 38,98</t>
+          <t>31,17; 38,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 18,81</t>
+          <t>12,88; 18,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,93; 29,54</t>
+          <t>23,71; 29,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,48; 40,91</t>
+          <t>34,33; 40,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,02; 37,57</t>
+          <t>31,53; 37,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,82; 27,28</t>
+          <t>15,88; 27,16</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,57; 33,57</t>
+          <t>21,0; 33,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,91; 47,82</t>
+          <t>32,6; 47,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,02; 45,77</t>
+          <t>31,9; 45,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,36; 25,81</t>
+          <t>15,26; 26,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,31; 32,26</t>
+          <t>19,33; 31,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,26; 49,23</t>
+          <t>34,13; 48,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,44; 49,99</t>
+          <t>35,36; 49,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,05; 24,26</t>
+          <t>13,84; 24,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,81; 30,34</t>
+          <t>21,89; 31,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,81; 46,24</t>
+          <t>36,37; 46,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,23; 44,96</t>
+          <t>35,56; 45,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,78; 23,43</t>
+          <t>15,35; 23,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,01; 31,4</t>
+          <t>24,72; 31,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,63; 41,85</t>
+          <t>34,52; 41,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,7; 38,41</t>
+          <t>31,79; 38,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,06; 30,87</t>
+          <t>16,81; 32,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,75; 30,83</t>
+          <t>25,14; 31,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,62; 41,6</t>
+          <t>35,17; 41,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,9; 40,52</t>
+          <t>34,37; 40,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,7; 19,61</t>
+          <t>14,54; 19,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,67; 30,21</t>
+          <t>25,75; 30,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,66; 40,63</t>
+          <t>35,53; 40,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,78; 38,66</t>
+          <t>33,94; 38,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,79; 24,46</t>
+          <t>16,66; 24,06</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17345; 29090</t>
+          <t>17443; 29521</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13327; 24918</t>
+          <t>13551; 25599</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8159; 17247</t>
+          <t>8343; 17183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3874; 12969</t>
+          <t>3798; 13140</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16437; 27483</t>
+          <t>15636; 27051</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16416; 29153</t>
+          <t>16623; 28903</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15524; 26806</t>
+          <t>15513; 27249</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9212; 22153</t>
+          <t>9383; 21389</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36431; 52702</t>
+          <t>36673; 52352</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33574; 49471</t>
+          <t>34256; 50149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25608; 40701</t>
+          <t>26764; 40797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15823; 32711</t>
+          <t>15538; 31007</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69307; 93989</t>
+          <t>69786; 95326</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101303; 129861</t>
+          <t>101869; 128818</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104361; 133374</t>
+          <t>104818; 134055</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77054; 180260</t>
+          <t>76840; 178132</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82141; 107890</t>
+          <t>82470; 109319</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>111657; 140235</t>
+          <t>111868; 141566</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>117858; 148081</t>
+          <t>118404; 147544</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65541; 97172</t>
+          <t>66551; 96974</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>158862; 196106</t>
+          <t>157440; 194637</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>222206; 263659</t>
+          <t>221254; 259726</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>232919; 273263</t>
+          <t>229369; 270805</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>154557; 266577</t>
+          <t>155181; 265359</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29457; 45857</t>
+          <t>28679; 45811</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38442; 55868</t>
+          <t>38085; 55448</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43553; 62253</t>
+          <t>43396; 61433</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22972; 38605</t>
+          <t>22823; 39053</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23859; 39851</t>
+          <t>23883; 39450</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48277; 67388</t>
+          <t>46724; 66757</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50996; 69945</t>
+          <t>49483; 68632</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25629; 44246</t>
+          <t>25239; 44383</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56735; 78934</t>
+          <t>56945; 80904</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90870; 117310</t>
+          <t>92287; 118275</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97211; 124066</t>
+          <t>98131; 125227</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52369; 77764</t>
+          <t>50942; 77171</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>125887; 158034</t>
+          <t>124435; 156383</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165150; 199619</t>
+          <t>164635; 199800</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166203; 201377</t>
+          <t>166664; 201612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113404; 205224</t>
+          <t>111726; 213673</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130804; 162956</t>
+          <t>132896; 166042</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>186550; 224109</t>
+          <t>189494; 224900</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>193596; 231374</t>
+          <t>196243; 232148</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>111905; 149274</t>
+          <t>110621; 151459</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>264926; 311705</t>
+          <t>265693; 313158</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>362249; 412672</t>
+          <t>360875; 412380</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>369934; 423452</t>
+          <t>371768; 424218</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>239320; 348796</t>
+          <t>237586; 342996</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42,13%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35,98%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40,62%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23,85%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>41,05%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>34,46%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>30,26%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>42,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,62%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,89; 52,28</t>
+          <t>30,93; 53,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,42; 46,14</t>
+          <t>25,89; 46,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,53; 42,28</t>
+          <t>29,17; 51,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 24,03</t>
+          <t>14,73; 35,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,44; 52,66</t>
+          <t>31,37; 52,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,77; 46,55</t>
+          <t>24,36; 45,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,28; 53,18</t>
+          <t>19,37; 43,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,13; 34,5</t>
+          <t>10,18; 29,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,01; 48,55</t>
+          <t>33,75; 49,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,14; 42,65</t>
+          <t>28,27; 42,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,13; 44,4</t>
+          <t>28,21; 44,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 26,57</t>
+          <t>14,8; 29,03</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>26,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>37,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>34,17%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,49; 30,72</t>
+          <t>23,27; 30,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 42,28</t>
+          <t>32,9; 42,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,16; 38,57</t>
+          <t>31,28; 38,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,69; 38,68</t>
+          <t>13,11; 19,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,32; 30,91</t>
+          <t>22,7; 30,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,92; 41,66</t>
+          <t>33,44; 42,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,17; 38,84</t>
+          <t>30,32; 38,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,88; 18,77</t>
+          <t>14,79; 21,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,71; 29,31</t>
+          <t>24,0; 29,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,33; 40,3</t>
+          <t>34,51; 40,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,53; 37,23</t>
+          <t>31,72; 37,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,88; 27,16</t>
+          <t>14,72; 19,51</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25,12%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42,02%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>42,62%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18,93%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>26,91%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>40,16%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>38,53%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,07%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,0; 33,54</t>
+          <t>18,88; 31,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,6; 47,46</t>
+          <t>35,6; 49,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,9; 45,16</t>
+          <t>36,42; 49,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,26; 26,11</t>
+          <t>13,87; 24,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,33; 31,93</t>
+          <t>20,73; 33,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,13; 48,76</t>
+          <t>33,06; 48,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,36; 49,05</t>
+          <t>31,65; 45,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 24,33</t>
+          <t>14,64; 26,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,89; 31,1</t>
+          <t>22,26; 30,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,37; 46,62</t>
+          <t>36,2; 46,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,56; 45,38</t>
+          <t>35,91; 45,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,35; 23,25</t>
+          <t>16,14; 23,5</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>28,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>35,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,72; 31,07</t>
+          <t>24,8; 31,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,52; 41,89</t>
+          <t>34,92; 41,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,79; 38,46</t>
+          <t>34,31; 40,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,81; 32,14</t>
+          <t>15,07; 20,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,14; 31,41</t>
+          <t>25,11; 31,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,17; 41,74</t>
+          <t>34,46; 41,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,37; 40,65</t>
+          <t>31,61; 38,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,9</t>
+          <t>16,01; 21,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,75; 30,35</t>
+          <t>25,76; 30,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,53; 40,6</t>
+          <t>35,81; 40,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,94; 38,73</t>
+          <t>33,97; 38,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 24,06</t>
+          <t>16,11; 19,86</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21644</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22342</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20814</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13530</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>23180</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>19122</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>12298</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7546</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21644</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22342</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20814</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22388</t>
+          <t>21835</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17443; 29521</t>
+          <t>15890; 27453</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13551; 25599</t>
+          <t>16073; 28625</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8343; 17183</t>
+          <t>14947; 26501</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3798; 13140</t>
+          <t>8356; 19891</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15636; 27051</t>
+          <t>17714; 29391</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16623; 28903</t>
+          <t>13515; 25249</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15513; 27249</t>
+          <t>7872; 17703</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9383; 21389</t>
+          <t>4761; 13779</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36673; 52352</t>
+          <t>36397; 53764</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34256; 50149</t>
+          <t>33233; 50168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26764; 40797</t>
+          <t>25921; 40445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15538; 31007</t>
+          <t>15312; 30047</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>181</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>112</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>94974</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>126269</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>132938</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76316</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>81521</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>115363</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>118753</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>103515</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94974</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>126269</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>132938</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81271</t>
+          <t>77128</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>184786</t>
+          <t>153443</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69786; 95326</t>
+          <t>82285; 109056</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101869; 128818</t>
+          <t>111807; 142963</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104818; 134055</t>
+          <t>118813; 147886</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76840; 178132</t>
+          <t>62351; 91745</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82470; 109319</t>
+          <t>70455; 94864</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>111868; 141566</t>
+          <t>101880; 130422</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>118404; 147544</t>
+          <t>105387; 134675</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66551; 96974</t>
+          <t>63971; 91917</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>157440; 194637</t>
+          <t>159324; 195226</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221254; 259726</t>
+          <t>222392; 262186</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>229369; 270805</t>
+          <t>230704; 272918</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>155181; 265359</t>
+          <t>133640; 177191</t>
         </is>
       </c>
     </row>
@@ -1784,37 +1784,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>31029</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57530</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59642</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31698</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>36754</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>46922</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>52411</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30009</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>31029</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57530</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>59642</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>61897</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28679; 45811</t>
+          <t>23321; 39333</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38085; 55448</t>
+          <t>48734; 67093</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43396; 61433</t>
+          <t>50969; 69527</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22823; 39053</t>
+          <t>23220; 41312</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23883; 39450</t>
+          <t>28311; 45895</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46724; 66757</t>
+          <t>38617; 56182</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49483; 68632</t>
+          <t>43049; 61462</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25239; 44383</t>
+          <t>21956; 39080</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56945; 80904</t>
+          <t>57901; 79472</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92287; 118275</t>
+          <t>91839; 117906</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98131; 125227</t>
+          <t>99088; 125749</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50942; 77171</t>
+          <t>51237; 74590</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>168</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>121544</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>141455</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>181408</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>183462</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>141069</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>147647</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>206142</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>213394</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>130218</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>271288</t>
+          <t>237175</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>124435; 156383</t>
+          <t>131055; 164091</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>164635; 199800</t>
+          <t>188165; 225055</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166664; 201612</t>
+          <t>195913; 233758</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111726; 213673</t>
+          <t>105481; 140487</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>132896; 166042</t>
+          <t>126371; 157231</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>189494; 224900</t>
+          <t>164366; 199035</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>196243; 232148</t>
+          <t>165689; 201641</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110621; 151459</t>
+          <t>100715; 134229</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>265693; 313158</t>
+          <t>265826; 312670</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360875; 412380</t>
+          <t>363763; 411236</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>371768; 424218</t>
+          <t>372034; 420792</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>237586; 342996</t>
+          <t>214098; 263885</t>
         </is>
       </c>
     </row>
